--- a/da_boyz/GroomsmenLetters26.xlsx
+++ b/da_boyz/GroomsmenLetters26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amasarie/Downloads/New Folder With Items/alex-and-sarah-wedhack26/da_boyz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED59B598-3D95-364E-AA26-8812B9328711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B7997D-9C0D-194F-AE7B-265960A6591E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="520" windowWidth="19680" windowHeight="11540" firstSheet="1" activeTab="6" xr2:uid="{31E93C6A-C918-1A44-8274-026410A1E83B}"/>
   </bookViews>
@@ -168,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -374,7 +374,15 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US"/>
-            <a:t>Matty B. and I have crossed paths with you before. Now we're getting married, and we've built something weird and joyful around it.</a:t>
+            <a:t>Matty B. and I have crossed paths with you before. Now Sarah</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" baseline="0"/>
+            <a:t> and I are</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t> getting married, and we've built something weird and joyful around it.</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1265,6 +1273,7 @@
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="TextBox 2">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E81F91B7-1991-C945-9C6A-5F5B1EE74EB5}"/>
@@ -1398,7 +1407,15 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US"/>
-            <a:t>, I'll send you the </a:t>
+            <a:t>, please</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" baseline="0"/>
+            <a:t> check </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t>the </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" b="1"/>
@@ -1406,7 +1423,15 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US"/>
-            <a:t>, where we can get into the ridiculous details, strategy, timing, costumes, bits, any prizes, and your opportunity to design your own glorious defeat.</a:t>
+            <a:t>, found</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" baseline="0"/>
+            <a:t> online at: https://github.com/mathfire/alex-and-sarah-wedhack26/da_boyz/</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US"/>
+            <a:t> where we can get into the ridiculous details, strategy, timing, costumes, bits, any prizes, and your opportunity to design your own glorious defeat.</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" baseline="0"/>
@@ -1754,7 +1779,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2DC490B-53D2-C344-A42F-8A6E9B9945F2}">
   <dimension ref="B1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="48.33203125" bestFit="1" customWidth="1"/>
@@ -1762,7 +1787,7 @@
     <col min="5" max="5" width="47.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:5">
       <c r="B1" t="s">
         <v>3</v>
       </c>
@@ -1776,7 +1801,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5">
       <c r="B2" t="s">
         <v>8</v>
       </c>
@@ -1790,7 +1815,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -1804,7 +1829,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5">
       <c r="B4" t="s">
         <v>12</v>
       </c>
@@ -1818,7 +1843,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -1832,7 +1857,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5">
       <c r="B6" t="s">
         <v>19</v>
       </c>
@@ -1846,7 +1871,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -1860,7 +1885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -1874,7 +1899,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5">
       <c r="B9" t="s">
         <v>21</v>
       </c>
@@ -1888,7 +1913,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:5">
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -1902,7 +1927,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:5">
       <c r="B11" t="s">
         <v>20</v>
       </c>
@@ -1916,7 +1941,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:5">
       <c r="B12" t="s">
         <v>4</v>
       </c>
@@ -1930,7 +1955,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:5">
       <c r="B13" t="s">
         <v>0</v>
       </c>
@@ -1944,7 +1969,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:5">
       <c r="B14" t="s">
         <v>1</v>
       </c>
@@ -1958,7 +1983,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:5">
       <c r="B15" t="s">
         <v>2</v>
       </c>
@@ -1972,7 +1997,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:5">
       <c r="B16" t="s">
         <v>7</v>
       </c>
@@ -1986,7 +2011,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:5">
       <c r="B17" t="s">
         <v>11</v>
       </c>
@@ -2000,7 +2025,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:5">
       <c r="B18" t="s">
         <v>13</v>
       </c>
@@ -2014,7 +2039,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:5">
       <c r="B19" t="s">
         <v>22</v>
       </c>
@@ -2028,7 +2053,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:5">
       <c r="B20" t="s">
         <v>10</v>
       </c>
@@ -2042,7 +2067,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:5">
       <c r="B21" t="s">
         <v>17</v>
       </c>
@@ -2056,7 +2081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:5">
       <c r="B22" t="s">
         <v>14</v>
       </c>
@@ -2070,7 +2095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:5">
       <c r="B23" t="s">
         <v>15</v>
       </c>
@@ -2101,7 +2126,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC1265FC-83E4-B149-96BB-62FA55EA7264}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2111,7 +2136,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0BDE6C4-CFEF-284C-8C17-25288D086E3E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2121,7 +2146,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E574DA3D-543C-8F49-B151-F8AE5BAFE566}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2131,7 +2156,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE7E75C-C6C6-A149-BE22-596E6CE1BF89}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2141,7 +2166,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{128F1479-BE28-244A-A7FA-D59C60511C5A}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2151,7 +2176,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F6CB2C-0C96-CA47-8187-CFDD46B20236}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
